--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E37EFC-FCCC-48D9-B850-EEDE7CE8254B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EAD7F2-C334-4F95-B817-25C1D097DCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{0A9D76D7-5577-49CE-9FAB-F5BCEF97040C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>date</t>
   </si>
@@ -143,16 +143,13 @@
     <t>https://drive.google.com/drive/folders/1RZYYptBGfCUlwNxCvLzEm97uj5K3GjPl?usp=drive_link</t>
   </si>
   <si>
-    <t>Romain;Enos;Seyed;Constantin;Joseph</t>
-  </si>
-  <si>
-    <t>Sofiane;Abdelkader;Amine;Mahdi;Wasim</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://drive.google.com/drive/folders/1rwS458lhBss-2t-SY0-VWxC2YDApoGlC?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Romain;Abdel Karim;Lamine;Joseph;Amine</t>
+  </si>
+  <si>
+    <t>Seyed;Mahdi;Youssef;Sofiane;Abdelkader</t>
   </si>
 </sst>
 </file>
@@ -795,19 +792,19 @@
         <v>45898</v>
       </c>
       <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="4">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="4">
+        <v>13</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EAD7F2-C334-4F95-B817-25C1D097DCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6548B4B-B16E-4E73-934A-D5C41DB3D433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{0A9D76D7-5577-49CE-9FAB-F5BCEF97040C}"/>
   </bookViews>
@@ -801,7 +801,7 @@
         <v>37</v>
       </c>
       <c r="E12" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>35</v>

--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6548B4B-B16E-4E73-934A-D5C41DB3D433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9FDC33-00C2-4840-9FFF-ED8858C7A94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{0A9D76D7-5577-49CE-9FAB-F5BCEF97040C}"/>
   </bookViews>

--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9FDC33-00C2-4840-9FFF-ED8858C7A94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6734357-4640-4707-9E1B-7FF06E27C71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{0A9D76D7-5577-49CE-9FAB-F5BCEF97040C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>date</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>Seyed;Mahdi;Youssef;Sofiane;Abdelkader</t>
+  </si>
+  <si>
+    <t>Constantin;Seyed;Youssef;Mahdi;Sofiane</t>
+  </si>
+  <si>
+    <t>Kevin;Aniss;Amine;Joseph;Wasim</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1-Hm-RBmkHTCXOJ4QFOx1H_h6ivoedbyR?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -557,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7531CF1B-E9A7-44AF-97FA-FCB344B04F1D}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="37.921875" bestFit="1" customWidth="1"/>
@@ -807,6 +816,26 @@
         <v>35</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>45905</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F4" r:id="rId1" xr:uid="{057F96AB-4123-4F5C-A334-7F117965C564}"/>
@@ -818,6 +847,7 @@
     <hyperlink ref="F9" r:id="rId7" xr:uid="{F8261502-E19A-4195-A10E-626FDD54AA28}"/>
     <hyperlink ref="F10" r:id="rId8" xr:uid="{F6B53448-54F0-4082-AD2B-C197764D5795}"/>
     <hyperlink ref="F11" r:id="rId9" xr:uid="{7F5A2705-9988-4214-8BB3-599A97DBBB7F}"/>
+    <hyperlink ref="F13" r:id="rId10" xr:uid="{F5445A9A-0F3E-4B83-9614-99F1B701A4EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6734357-4640-4707-9E1B-7FF06E27C71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6265ECF9-2F66-4EF2-B80A-522D74A4452F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{0A9D76D7-5577-49CE-9FAB-F5BCEF97040C}"/>
   </bookViews>
@@ -824,7 +824,7 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
         <v>39</v>

--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -7,11 +7,16 @@
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gpDWgeDqdZvS50+NELsSgu/5nBXHULP9wumoEwgLZ6k="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>date</t>
   </si>
@@ -219,6 +224,15 @@
     </r>
   </si>
   <si>
+    <t>Florent;Lamine;Driss;Aniss;Abdel Karim</t>
+  </si>
+  <si>
+    <t>Abderrhman;Nizar;Joseph;Mahdi;Mario</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/16vu79gj0Kjv8fSqsk49B4I16V2waorAL?usp=drive_link</t>
+  </si>
+  <si>
     <t>Constantin;Seyed;Wassim;Loic;François</t>
   </si>
   <si>
@@ -235,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -270,6 +284,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -299,30 +319,39 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +564,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.13"/>
     <col customWidth="1" min="2" max="2" width="39.38"/>
@@ -545,7 +574,7 @@
     <col customWidth="1" min="6" max="6" width="136.0"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2">
         <v>45783.0</v>
       </c>
@@ -585,7 +614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2">
         <v>45791.0</v>
       </c>
@@ -605,7 +634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2">
         <v>45793.0</v>
       </c>
@@ -625,7 +654,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2">
         <v>45797.0</v>
       </c>
@@ -645,7 +674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2">
         <v>45798.0</v>
       </c>
@@ -665,11 +694,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2">
         <v>45800.0</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="3">
@@ -685,7 +714,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2">
         <v>45804.0</v>
       </c>
@@ -705,7 +734,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2">
         <v>45814.0</v>
       </c>
@@ -725,7 +754,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2">
         <v>45884.0</v>
       </c>
@@ -745,7 +774,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2">
         <v>45891.0</v>
       </c>
@@ -765,7 +794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2">
         <v>45898.0</v>
       </c>
@@ -785,8 +814,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="7">
         <v>45905.0</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -805,26 +834,1032 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="8">
+        <v>45925.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="7">
         <v>45926.0</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="10">
         <v>13.0</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="7">
+      <c r="D15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="10">
         <v>14.0</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>44</v>
+      <c r="F15" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
@@ -840,7 +1875,8 @@
     <hyperlink r:id="rId11" ref="F12"/>
     <hyperlink r:id="rId12" ref="F13"/>
     <hyperlink r:id="rId13" ref="F14"/>
+    <hyperlink r:id="rId14" ref="F15"/>
   </hyperlinks>
-  <drawing r:id="rId14"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -7,16 +7,11 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gpDWgeDqdZvS50+NELsSgu/5nBXHULP9wumoEwgLZ6k="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>date</t>
   </si>
@@ -34,6 +29,9 @@
   </si>
   <si>
     <t>Lien</t>
+  </si>
+  <si>
+    <t>Timeline</t>
   </si>
   <si>
     <t>Constantin;Enos;François;Stephane;Seyed</t>
@@ -241,6 +239,70 @@
   <si>
     <t>https://drive.google.com/drive/folders/14UK_QOTGM6Nml6nDTzIffvejBUSL4Y72?usp=sharing</t>
   </si>
+  <si>
+    <t>["9'", 'Kevin', 'Team A 0–1 Team B']
+["9'", 'Mahdi', 'Team A 0–2 Team B']
+["14'", 'Loic', 'Team A 1–2 Team B']
+["14'", 'Anasse', 'Team A 1–3 Team B']
+["15'", 'Constantin', 'Team A 2–3 Team B']
+["26'", 'Seyed', 'Team A 3–3 Team B']
+["28'", 'Romain', 'Team A 3–4 Team B']
+["28'", 'Wassim', 'Team A 4–4 Team B']
+["29'", 'Mahdi', 'Team A 4–5 Team B']
+["32'", 'Loic', 'Team A 5–5 Team B']
+["34'", 'Anasse', 'Team A 5–6 Team B']
+["37'", 'Wassim', 'Team A 6–6 Team B']
+["41'", 'Loic', 'Team A 7–6 Team B']
+["44'", 'Mahdi', 'Team A 7–7 Team B']
+["45'", 'Wassim', 'Team A 8–7 Team B']
+["47'", 'Kevin', 'Team A 8–8 Team B']
+["47'", 'Constantin', 'Team A 9–8 Team B']
+["49'", 'Loic', 'Team A 10–8 Team B']
+["49'", 'Kevin', 'Team A 10–9 Team B']
+["50'", 'Kevin', 'Team A 10–10 Team B']
+["51'", 'Romain', 'Team A 10–11 Team B']
+["52'", 'Wassim', 'Team A 11–11 Team B']
+["52'", 'Romain', 'Team A 11–12 Team B']
+["53'", 'Loic', 'Team A 12–12 Team B']
+["55'", 'Kevin', 'Team A 12–13 Team B']
+["57'", 'François', 'Team A 13–13 Team B']
+["57'", 'Mahdi', 'Team A 13–14 Team B']</t>
+  </si>
+  <si>
+    <t>Constantin;Enos;Jesus;Loic;Mohamed</t>
+  </si>
+  <si>
+    <t>Anasse;Driss;Florent;Aniss;Lamine</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1uTGn0YMUkgTue4u3Y5-3HPyNH8wStzIv?usp=drive_link</t>
+  </si>
+  <si>
+    <t>["7'", 'Lamine', 'Team A 0–1 Team B']
+["8'", 'Loic', 'Team A 1–1 Team B']
+["10'", 'Lamine', 'Team A 1–2 Team B']
+["13'", 'Lamine', 'Team A 1–3 Team B']
+["17'", 'Loic', 'Team A 2–3 Team B']
+["18'", 'Enos', 'Team A 3–3 Team B']
+["18'", 'Anasse', 'Team A 3–4 Team B']
+["19'", 'Lamine', 'Team A 3–5 Team B']
+["22'", 'Jesus', 'Team A 4–5 Team B']
+["24'", 'Mohamed', 'Team A 5–5 Team B']
+["25'", 'Driss', 'Team A 5–6 Team B']
+["26'", 'Enos', 'Team A 6–6 Team B']
+["29'", 'Loic', 'Team A 7–6 Team B']
+["34'", 'Lamine', 'Team A 7–7 Team B']
+["36'", 'Anasse', 'Team A 7–8 Team B']
+["40'", 'aniss', 'Team A 7–9 Team B']
+["41'", 'Mohamed', 'Team A 8–9 Team B']
+["41'", 'Anasse', 'Team A 8–10 Team B']
+["43'", 'Florent', 'Team A 8–11 Team B']
+["44'", 'Loic', 'Team A 9–11 Team B']
+["47'", 'Constantin', 'Team A 10–11 Team B']
+["50'", 'Aniss', 'Team A 10–12 Team B']
+["52'", 'Florent', 'Team A 10–13 Team B']
+["56'", 'Driss', 'Team A 10–14 Team B']</t>
+  </si>
 </sst>
 </file>
 
@@ -249,7 +311,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -290,6 +352,11 @@
       <color rgb="FF0000FF"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -319,12 +386,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -352,6 +422,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,7 +644,7 @@
     <col customWidth="1" min="3" max="3" width="6.63"/>
     <col customWidth="1" min="4" max="4" width="39.0"/>
     <col customWidth="1" min="5" max="5" width="6.63"/>
-    <col customWidth="1" min="6" max="6" width="136.0"/>
+    <col customWidth="1" min="6" max="6" width="81.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -593,288 +666,316 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>45783.0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4">
         <v>12.0</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4">
         <v>11.0</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>45791.0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
         <v>7.0</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4">
         <v>10.0</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>45793.0</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4">
         <v>9.0</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4">
         <v>8.0</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>14</v>
+      <c r="F4" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>45797.0</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
         <v>11.0</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="4">
         <v>15.0</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>17</v>
+      <c r="F5" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>45798.0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4">
         <v>11.0</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="D6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4">
         <v>9.0</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>20</v>
+      <c r="F6" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>45800.0</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4">
         <v>12.0</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4">
         <v>10.0</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>23</v>
+      <c r="F7" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>45804.0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4">
         <v>12.0</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4">
         <v>8.0</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>26</v>
+      <c r="F8" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>45814.0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4">
         <v>8.0</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4">
         <v>10.0</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>29</v>
+      <c r="F9" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>45884.0</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4">
         <v>13.0</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="4">
         <v>12.0</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>32</v>
+      <c r="F10" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45891.0</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4">
         <v>13.0</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="D11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="4">
         <v>15.0</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>35</v>
+      <c r="F11" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45898.0</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="4">
         <v>12.0</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="4">
         <v>12.0</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>38</v>
+      <c r="F12" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>45905.0</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4">
         <v>13.0</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="D13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="4">
         <v>13.0</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>41</v>
+      <c r="F13" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>45925.0</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="B14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7">
         <v>11.0</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="D14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="7">
         <v>10.0</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>44</v>
+      <c r="F14" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="7">
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="8">
         <v>45926.0</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="10">
+      <c r="B15" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="11">
         <v>13.0</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="10">
+      <c r="D15" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="11">
         <v>14.0</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>47</v>
+      <c r="F15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="9">
+        <v>45939.0</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="11">
+        <v>14.0</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -1876,7 +1977,8 @@
     <hyperlink r:id="rId12" ref="F13"/>
     <hyperlink r:id="rId13" ref="F14"/>
     <hyperlink r:id="rId14" ref="F15"/>
+    <hyperlink r:id="rId15" ref="F16"/>
   </hyperlinks>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Feuil1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="videos" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -31,7 +31,7 @@
     <t>Lien</t>
   </si>
   <si>
-    <t>Timeline</t>
+    <t>timeline</t>
   </si>
   <si>
     <t>Constantin;Enos;François;Stephane;Seyed</t>
@@ -240,33 +240,8 @@
     <t>https://drive.google.com/drive/folders/14UK_QOTGM6Nml6nDTzIffvejBUSL4Y72?usp=sharing</t>
   </si>
   <si>
-    <t>["9'", 'Kevin', 'Team A 0–1 Team B']
-["9'", 'Mahdi', 'Team A 0–2 Team B']
-["14'", 'Loic', 'Team A 1–2 Team B']
-["14'", 'Anasse', 'Team A 1–3 Team B']
-["15'", 'Constantin', 'Team A 2–3 Team B']
-["26'", 'Seyed', 'Team A 3–3 Team B']
-["28'", 'Romain', 'Team A 3–4 Team B']
-["28'", 'Wassim', 'Team A 4–4 Team B']
-["29'", 'Mahdi', 'Team A 4–5 Team B']
-["32'", 'Loic', 'Team A 5–5 Team B']
-["34'", 'Anasse', 'Team A 5–6 Team B']
-["37'", 'Wassim', 'Team A 6–6 Team B']
-["41'", 'Loic', 'Team A 7–6 Team B']
-["44'", 'Mahdi', 'Team A 7–7 Team B']
-["45'", 'Wassim', 'Team A 8–7 Team B']
-["47'", 'Kevin', 'Team A 8–8 Team B']
-["47'", 'Constantin', 'Team A 9–8 Team B']
-["49'", 'Loic', 'Team A 10–8 Team B']
-["49'", 'Kevin', 'Team A 10–9 Team B']
-["50'", 'Kevin', 'Team A 10–10 Team B']
-["51'", 'Romain', 'Team A 10–11 Team B']
-["52'", 'Wassim', 'Team A 11–11 Team B']
-["52'", 'Romain', 'Team A 11–12 Team B']
-["53'", 'Loic', 'Team A 12–12 Team B']
-["55'", 'Kevin', 'Team A 12–13 Team B']
-["57'", 'François', 'Team A 13–13 Team B']
-["57'", 'Mahdi', 'Team A 13–14 Team B']</t>
+    <t>9,Kevin,0-1; 9,Mahdi,0-2; 14,Loic,1-2; 14,Anasse,1-3; 15,Constantin,2-3; 26,Seyed,3-3; 28,Romain,3-4; 28,Wassim,4-4; 29,Mahdi,4-5; 32,Loic,5-5; 34,Anasse,5-6; 37,Wassim,6-6; 41,Loic,7-6; 44,Mahdi,7-7; 45,Wassim,8-7; 47,Kevin,8-8; 47,Constantin,9-8; 49,Loic,10-8; 49,Kevin,10-9; 50,Kevin,10-10; 51,Romain,10-11; 52,Wassim,11-11; 52,Romain,11-12; 53,Loic,12-12
+55,Kevin,12-13; 57,François,13-13; 57,Mahdi,13-14</t>
   </si>
   <si>
     <t>Constantin;Enos;Jesus;Loic;Mohamed</t>
@@ -278,30 +253,7 @@
     <t>https://drive.google.com/drive/folders/1uTGn0YMUkgTue4u3Y5-3HPyNH8wStzIv?usp=drive_link</t>
   </si>
   <si>
-    <t>["7'", 'Lamine', 'Team A 0–1 Team B']
-["8'", 'Loic', 'Team A 1–1 Team B']
-["10'", 'Lamine', 'Team A 1–2 Team B']
-["13'", 'Lamine', 'Team A 1–3 Team B']
-["17'", 'Loic', 'Team A 2–3 Team B']
-["18'", 'Enos', 'Team A 3–3 Team B']
-["18'", 'Anasse', 'Team A 3–4 Team B']
-["19'", 'Lamine', 'Team A 3–5 Team B']
-["22'", 'Jesus', 'Team A 4–5 Team B']
-["24'", 'Mohamed', 'Team A 5–5 Team B']
-["25'", 'Driss', 'Team A 5–6 Team B']
-["26'", 'Enos', 'Team A 6–6 Team B']
-["29'", 'Loic', 'Team A 7–6 Team B']
-["34'", 'Lamine', 'Team A 7–7 Team B']
-["36'", 'Anasse', 'Team A 7–8 Team B']
-["40'", 'aniss', 'Team A 7–9 Team B']
-["41'", 'Mohamed', 'Team A 8–9 Team B']
-["41'", 'Anasse', 'Team A 8–10 Team B']
-["43'", 'Florent', 'Team A 8–11 Team B']
-["44'", 'Loic', 'Team A 9–11 Team B']
-["47'", 'Constantin', 'Team A 10–11 Team B']
-["50'", 'Aniss', 'Team A 10–12 Team B']
-["52'", 'Florent', 'Team A 10–13 Team B']
-["56'", 'Driss', 'Team A 10–14 Team B']</t>
+    <t>7,Lamine,0-1; 8,Loic,1-1; 10,Lamine,1-2; 13,Lamine,1-3; 17,Loic,2-3; 18,Enos,3-3; 18,Anasse,3-4; 19,Lamine,3-5; 22,Jesus,4-5; 24,Mohamed,5-5; 25,Driss,5-6; 26,Enos,6-6; 29,Loic,7-6; 34,Lamine,7-7; 36,Anasse,7-8; 40,aniss,7-9; 41,Mohamed,8-9; 41,Anasse,8-10; 43,Florent,8-11; 44,Loic,9-11; 47,Constantin,10-11; 50,Aniss,10-12; 52,Florent,10-13; 56,Driss,10-14</t>
   </si>
 </sst>
 </file>
@@ -386,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -422,6 +374,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
@@ -645,6 +600,7 @@
     <col customWidth="1" min="4" max="4" width="39.0"/>
     <col customWidth="1" min="5" max="5" width="6.63"/>
     <col customWidth="1" min="6" max="6" width="81.25"/>
+    <col customWidth="1" min="7" max="7" width="276.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -972,7 +928,7 @@
       <c r="F16" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="13" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/videos.xlsx
+++ b/data/videos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>date</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/16vu79gj0Kjv8fSqsk49B4I16V2waorAL?usp=drive_link</t>
+  </si>
+  <si>
+    <t>1,Florent,1-0;4,Florent,2-0;7,Nizar,2-1;8,Nizar,2-2;11,Florent,3-2;15,Nizar,3-3;16,Florent,4-3;17,Nizar,4-4;20,Florent,5-4;29,Florent,6-4;31,Florent,7-4;32,Nizar,7-5;37,Nizar,7-6;40,Nizar,7-7;41,Florent,8-7;42,Nizar,8-8;46,Nizar,8-9;47,Florent,9-9;48,Florent,10-9;49,Nizar,10-10;58,Florent,11-10</t>
   </si>
   <si>
     <t>Constantin;Seyed;Wassim;Loic;François</t>
@@ -338,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -371,6 +374,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -885,28 +891,31 @@
       <c r="F14" s="10" t="s">
         <v>45</v>
       </c>
+      <c r="G14" s="11" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="8">
         <v>45926.0</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="11">
+      <c r="B15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="12">
         <v>13.0</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="11">
+      <c r="D15" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="12">
         <v>14.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="12" t="s">
         <v>49</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -914,28 +923,30 @@
         <v>45939.0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="7">
         <v>10.0</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="11">
+        <v>52</v>
+      </c>
+      <c r="E16" s="12">
         <v>14.0</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="13" t="s">
         <v>53</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="B20" s="13"/>
+    </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
